--- a/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/consolidado_ingresos.xlsx
+++ b/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/consolidado_ingresos.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J272"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6470,24 +6470,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E127" t="n">
-        <v>4021409.53</v>
+        <v>4901740.86</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -6501,12 +6501,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6518,24 +6518,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E128" t="n">
-        <v>2582093.02</v>
+        <v>3850739.8</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6566,24 +6566,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E129" t="n">
-        <v>3555194.75</v>
+        <v>229146.83</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6592,17 +6592,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6614,24 +6614,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E130" t="n">
-        <v>295894.16</v>
+        <v>374182.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6662,24 +6662,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E131" t="n">
-        <v>3071022.19</v>
+        <v>77768.99000000001</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6710,24 +6710,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E132" t="n">
-        <v>2454066.23</v>
+        <v>3536931.6</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6736,17 +6736,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6758,24 +6758,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E133" t="n">
-        <v>4028797.51</v>
+        <v>4950100.02</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6784,17 +6784,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6806,24 +6806,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E134" t="n">
-        <v>1753810.37</v>
+        <v>2516792.1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6832,17 +6832,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6854,24 +6854,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E135" t="n">
-        <v>418669</v>
+        <v>3996853.26</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6880,17 +6880,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6902,24 +6902,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E136" t="n">
-        <v>189994.64</v>
+        <v>514373.04</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6928,17 +6928,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6950,24 +6950,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E137" t="n">
-        <v>2525232.67</v>
+        <v>257205.56</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6976,17 +6976,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6998,24 +6998,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E138" t="n">
-        <v>1891849.04</v>
+        <v>3666171.14</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -7024,17 +7024,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7046,24 +7046,24 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E139" t="n">
-        <v>476547.8</v>
+        <v>663456.97</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7094,24 +7094,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E140" t="n">
-        <v>3846380.14</v>
+        <v>1657661.35</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7142,24 +7142,24 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E141" t="n">
-        <v>2896517.18</v>
+        <v>4595149.11</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -7168,17 +7168,17 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7190,24 +7190,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E142" t="n">
-        <v>2052706.92</v>
+        <v>137126.41</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -7216,17 +7216,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7238,24 +7238,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E143" t="n">
-        <v>868322.61</v>
+        <v>4158973.39</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -7264,17 +7264,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7286,24 +7286,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="E144" t="n">
-        <v>3907516.26</v>
+        <v>3796006.26</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -7317,12 +7317,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7334,24 +7334,24 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Prima cobrada neta</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4120</v>
+        <v>4310</v>
       </c>
       <c r="E145" t="n">
-        <v>2903402.12</v>
+        <v>4396843.82</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -7360,17 +7360,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7382,24 +7382,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4120</v>
+        <v>4230</v>
       </c>
       <c r="E146" t="n">
-        <v>4041211.21</v>
+        <v>4491149.94</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -7408,17 +7408,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7430,24 +7430,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="E147" t="n">
-        <v>4498833.7</v>
+        <v>1009071.05</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -7456,17 +7456,17 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -7478,24 +7478,24 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4410</v>
+        <v>4110</v>
       </c>
       <c r="E148" t="n">
-        <v>228864.37</v>
+        <v>3683469.74</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -7504,17 +7504,17 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -7526,24 +7526,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4120</v>
+        <v>4140</v>
       </c>
       <c r="E149" t="n">
-        <v>4245227.26</v>
+        <v>4311812.65</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -7552,17 +7552,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -7574,25 +7574,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4410</v>
-      </c>
-      <c r="E150" t="n">
-        <v>788629.6</v>
-      </c>
+        <v>4230</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>Ingreso</t>
@@ -7600,17 +7598,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7622,24 +7620,24 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4410</v>
+        <v>4110</v>
       </c>
       <c r="E151" t="n">
-        <v>2962519.16</v>
+        <v>1068515.85</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7648,17 +7646,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7670,24 +7668,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4410</v>
+        <v>4230</v>
       </c>
       <c r="E152" t="n">
-        <v>2152293.44</v>
+        <v>1711196.89</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7696,7 +7694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7706,7 +7704,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7718,24 +7716,24 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E153" t="n">
-        <v>4901740.86</v>
+        <v>4957857.82</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7744,17 +7742,17 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -7766,24 +7764,24 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4310</v>
+        <v>4230</v>
       </c>
       <c r="E154" t="n">
-        <v>3850739.8</v>
+        <v>300097.71</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7792,17 +7790,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -7814,24 +7812,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E155" t="n">
-        <v>229146.83</v>
+        <v>4754235.53</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7845,12 +7843,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -7862,24 +7860,24 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E156" t="n">
-        <v>374182.5</v>
+        <v>1603932.54</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7888,17 +7886,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7910,24 +7908,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E157" t="n">
-        <v>77768.99000000001</v>
+        <v>4809986.55</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7936,17 +7934,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -7958,24 +7956,24 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E158" t="n">
-        <v>3536931.6</v>
+        <v>4646162.65</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7989,12 +7987,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8006,24 +8004,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E159" t="n">
-        <v>4950100.02</v>
+        <v>2408155.69</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -8037,12 +8035,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8054,24 +8052,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E160" t="n">
-        <v>2516792.1</v>
+        <v>1123620.63</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -8085,12 +8083,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -8102,24 +8100,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E161" t="n">
-        <v>3996853.26</v>
+        <v>3704788.01</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -8133,12 +8131,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -8150,24 +8148,24 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4310</v>
+        <v>4230</v>
       </c>
       <c r="E162" t="n">
-        <v>514373.04</v>
+        <v>1781587.24</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -8176,7 +8174,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8186,7 +8184,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8198,24 +8196,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4310</v>
+        <v>4230</v>
       </c>
       <c r="E163" t="n">
-        <v>257205.56</v>
+        <v>1978735.39</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -8229,12 +8227,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8246,24 +8244,24 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E164" t="n">
-        <v>3666171.14</v>
+        <v>2261349.46</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -8272,17 +8270,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8294,24 +8292,24 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E165" t="n">
-        <v>663456.97</v>
+        <v>1397816.34</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -8320,17 +8318,17 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -8342,24 +8340,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4310</v>
+        <v>4110</v>
       </c>
       <c r="E166" t="n">
-        <v>1657661.35</v>
+        <v>1305727</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -8373,12 +8371,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8390,24 +8388,24 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4310</v>
+        <v>4230</v>
       </c>
       <c r="E167" t="n">
-        <v>4595149.11</v>
+        <v>3965446.65</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -8416,17 +8414,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -8438,24 +8436,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4310</v>
+        <v>4140</v>
       </c>
       <c r="E168" t="n">
-        <v>137126.41</v>
+        <v>1718705.33</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -8464,17 +8462,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -8486,24 +8484,24 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4310</v>
+        <v>4230</v>
       </c>
       <c r="E169" t="n">
-        <v>4158973.39</v>
+        <v>3519225.22</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -8522,7 +8520,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -8534,24 +8532,24 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4310</v>
+        <v>4110</v>
       </c>
       <c r="E170" t="n">
-        <v>3796006.26</v>
+        <v>1322092.72</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -8565,12 +8563,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -8582,24 +8580,24 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prima cobrada neta</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4310</v>
+        <v>4120</v>
       </c>
       <c r="E171" t="n">
-        <v>4396843.82</v>
+        <v>822504.49</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -8608,17 +8606,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>seguros.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -8630,7 +8628,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8640,14 +8638,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4230</v>
+        <v>4140</v>
       </c>
       <c r="E172" t="n">
-        <v>4491149.94</v>
+        <v>4085798.79</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -8656,7 +8654,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8678,7 +8676,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8688,14 +8686,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4110</v>
+        <v>4120</v>
       </c>
       <c r="E173" t="n">
-        <v>1009071.05</v>
+        <v>2548378.36</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8704,12 +8702,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8726,7 +8724,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8743,7 +8741,7 @@
         <v>4110</v>
       </c>
       <c r="E174" t="n">
-        <v>3683469.74</v>
+        <v>4710900.79</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -8752,12 +8750,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8774,7 +8772,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8784,14 +8782,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4140</v>
+        <v>4120</v>
       </c>
       <c r="E175" t="n">
-        <v>4311812.65</v>
+        <v>3905605.21</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8800,12 +8798,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8822,7 +8820,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8838,7 +8836,9 @@
       <c r="D176" t="n">
         <v>4230</v>
       </c>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="n">
+        <v>297311.26</v>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>Ingreso</t>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8868,7 +8868,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8878,14 +8878,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4110</v>
+        <v>4230</v>
       </c>
       <c r="E177" t="n">
-        <v>1068515.85</v>
+        <v>3255146.81</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8926,14 +8926,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>4230</v>
+        <v>4140</v>
       </c>
       <c r="E178" t="n">
-        <v>1711196.89</v>
+        <v>801827.1</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8942,12 +8942,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8964,7 +8964,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8974,14 +8974,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4120</v>
+        <v>4230</v>
       </c>
       <c r="E179" t="n">
-        <v>4957857.82</v>
+        <v>2887780.37</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9022,14 +9022,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4230</v>
+        <v>4120</v>
       </c>
       <c r="E180" t="n">
-        <v>300097.71</v>
+        <v>1391873.55</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9060,7 +9060,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9070,14 +9070,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4120</v>
+        <v>4230</v>
       </c>
       <c r="E181" t="n">
-        <v>4754235.53</v>
+        <v>1075228.08</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9108,7 +9108,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9125,7 +9125,7 @@
         <v>4140</v>
       </c>
       <c r="E182" t="n">
-        <v>1603932.54</v>
+        <v>726062.75</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9156,7 +9156,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9173,7 +9173,7 @@
         <v>4140</v>
       </c>
       <c r="E183" t="n">
-        <v>4809986.55</v>
+        <v>4282828.88</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9204,7 +9204,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9214,14 +9214,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="E184" t="n">
-        <v>4646162.65</v>
+        <v>889558.3199999999</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -9230,12 +9230,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9252,7 +9252,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9262,14 +9262,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4140</v>
+        <v>4120</v>
       </c>
       <c r="E185" t="n">
-        <v>2408155.69</v>
+        <v>1620600.07</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9300,7 +9300,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9317,7 +9317,7 @@
         <v>4120</v>
       </c>
       <c r="E186" t="n">
-        <v>1123620.63</v>
+        <v>4717844.96</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -9326,12 +9326,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9348,7 +9348,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9358,14 +9358,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="E187" t="n">
-        <v>3704788.01</v>
+        <v>4301179.73</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9406,14 +9406,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4230</v>
+        <v>4120</v>
       </c>
       <c r="E188" t="n">
-        <v>1781587.24</v>
+        <v>3905072.78</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9444,7 +9444,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9461,7 +9461,7 @@
         <v>4230</v>
       </c>
       <c r="E189" t="n">
-        <v>1978735.39</v>
+        <v>3187163.56</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -9470,12 +9470,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9492,7 +9492,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9502,14 +9502,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4140</v>
+        <v>4120</v>
       </c>
       <c r="E190" t="n">
-        <v>2261349.46</v>
+        <v>3407092.84</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -9518,12 +9518,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9540,7 +9540,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9550,14 +9550,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4120</v>
+        <v>4140</v>
       </c>
       <c r="E191" t="n">
-        <v>1397816.34</v>
+        <v>4124235.95</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9588,7 +9588,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9598,14 +9598,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4110</v>
+        <v>4120</v>
       </c>
       <c r="E192" t="n">
-        <v>1305727</v>
+        <v>6660.22</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9636,7 +9636,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9646,14 +9646,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4230</v>
+        <v>4110</v>
       </c>
       <c r="E193" t="n">
-        <v>3965446.65</v>
+        <v>3621789.23</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9694,14 +9694,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>4140</v>
+        <v>4120</v>
       </c>
       <c r="E194" t="n">
-        <v>1718705.33</v>
+        <v>564537.6</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9732,7 +9732,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9749,7 +9749,7 @@
         <v>4230</v>
       </c>
       <c r="E195" t="n">
-        <v>3519225.22</v>
+        <v>257608.45</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -9758,12 +9758,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9780,7 +9780,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9790,14 +9790,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>4110</v>
+        <v>4230</v>
       </c>
       <c r="E196" t="n">
-        <v>1322092.72</v>
+        <v>3812692.48</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9838,14 +9838,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="E197" t="n">
-        <v>822504.49</v>
+        <v>4286904.6</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9876,7 +9876,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9886,14 +9886,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4140</v>
+        <v>4120</v>
       </c>
       <c r="E198" t="n">
-        <v>4085798.79</v>
+        <v>3462880.13</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9924,7 +9924,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9934,14 +9934,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="E199" t="n">
-        <v>2548378.36</v>
+        <v>2289552.86</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9972,7 +9972,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9982,14 +9982,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Intereses tarjeta crédito</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4110</v>
+        <v>4230</v>
       </c>
       <c r="E200" t="n">
-        <v>4710900.79</v>
+        <v>1547816.5</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10030,14 +10030,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>4120</v>
+        <v>4140</v>
       </c>
       <c r="E201" t="n">
-        <v>3905605.21</v>
+        <v>486007.7</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -10046,12 +10046,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10068,7 +10068,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>4230</v>
+        <v>4110</v>
       </c>
       <c r="E202" t="n">
-        <v>297311.26</v>
+        <v>3466332.33</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10116,7 +10116,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10126,14 +10126,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4230</v>
+        <v>4120</v>
       </c>
       <c r="E203" t="n">
-        <v>3255146.81</v>
+        <v>922639.21</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10164,7 +10164,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10181,7 +10181,7 @@
         <v>4140</v>
       </c>
       <c r="E204" t="n">
-        <v>801827.1</v>
+        <v>599209.9399999999</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10229,7 +10229,7 @@
         <v>4230</v>
       </c>
       <c r="E205" t="n">
-        <v>2887780.37</v>
+        <v>4171160.15</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -10238,12 +10238,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10260,24 +10260,24 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E206" t="n">
-        <v>1391873.55</v>
+        <v>4665656.44</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -10291,12 +10291,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10308,24 +10308,24 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4230</v>
+        <v>4210</v>
       </c>
       <c r="E207" t="n">
-        <v>1075228.08</v>
+        <v>796930.42</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -10334,17 +10334,17 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -10356,24 +10356,24 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="E208" t="n">
-        <v>726062.75</v>
+        <v>2367461.18</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -10382,17 +10382,17 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -10404,24 +10404,24 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="E209" t="n">
-        <v>4282828.88</v>
+        <v>2911083.68</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -10430,17 +10430,17 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -10452,24 +10452,24 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>4110</v>
+        <v>4130</v>
       </c>
       <c r="E210" t="n">
-        <v>889558.3199999999</v>
+        <v>981062.92</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -10500,24 +10500,24 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4120</v>
+        <v>4130</v>
       </c>
       <c r="E211" t="n">
-        <v>1620600.07</v>
+        <v>3614973.5</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -10526,17 +10526,17 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -10548,24 +10548,24 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E212" t="n">
-        <v>4717844.96</v>
+        <v>1899435.91</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -10579,12 +10579,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -10596,24 +10596,24 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>4110</v>
+        <v>4210</v>
       </c>
       <c r="E213" t="n">
-        <v>4301179.73</v>
+        <v>1683507.73</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -10644,24 +10644,24 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E214" t="n">
-        <v>3905072.78</v>
+        <v>3266632.55</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -10675,12 +10675,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -10692,24 +10692,24 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4230</v>
+        <v>4210</v>
       </c>
       <c r="E215" t="n">
-        <v>3187163.56</v>
+        <v>4740042.61</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -10718,17 +10718,17 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -10740,24 +10740,24 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E216" t="n">
-        <v>3407092.84</v>
+        <v>4244288.36</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -10766,17 +10766,17 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -10788,24 +10788,24 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="E217" t="n">
-        <v>4124235.95</v>
+        <v>561709.38</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -10836,24 +10836,24 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4120</v>
+        <v>4130</v>
       </c>
       <c r="E218" t="n">
-        <v>6660.22</v>
+        <v>4425606</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -10862,17 +10862,17 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -10884,24 +10884,24 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>4110</v>
+        <v>4210</v>
       </c>
       <c r="E219" t="n">
-        <v>3621789.23</v>
+        <v>3388125.65</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10910,17 +10910,17 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -10932,24 +10932,24 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E220" t="n">
-        <v>564537.6</v>
+        <v>1696985.84</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -10980,24 +10980,24 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>4230</v>
+        <v>4210</v>
       </c>
       <c r="E221" t="n">
-        <v>257608.45</v>
+        <v>4390186.28</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -11028,24 +11028,24 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4230</v>
+        <v>4130</v>
       </c>
       <c r="E222" t="n">
-        <v>3812692.48</v>
+        <v>1735882.89</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -11059,12 +11059,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -11076,24 +11076,24 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>4110</v>
+        <v>4130</v>
       </c>
       <c r="E223" t="n">
-        <v>4286904.6</v>
+        <v>736957.61</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -11107,12 +11107,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -11124,24 +11124,24 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>4120</v>
+        <v>4130</v>
       </c>
       <c r="E224" t="n">
-        <v>3462880.13</v>
+        <v>4980240.9</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -11172,24 +11172,24 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4110</v>
+        <v>4210</v>
       </c>
       <c r="E225" t="n">
-        <v>2289552.86</v>
+        <v>1831652.89</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -11220,24 +11220,24 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4230</v>
+        <v>4210</v>
       </c>
       <c r="E226" t="n">
-        <v>1547816.5</v>
+        <v>1242302.43</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -11246,17 +11246,17 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -11268,24 +11268,24 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="E227" t="n">
-        <v>486007.7</v>
+        <v>3324582.34</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -11294,17 +11294,17 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -11316,24 +11316,24 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>4110</v>
+        <v>4130</v>
       </c>
       <c r="E228" t="n">
-        <v>3466332.33</v>
+        <v>113230.09</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -11364,24 +11364,24 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4120</v>
+        <v>4210</v>
       </c>
       <c r="E229" t="n">
-        <v>922639.21</v>
+        <v>1255816.07</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -11390,17 +11390,17 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -11412,24 +11412,24 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="E230" t="n">
-        <v>599209.9399999999</v>
+        <v>2832871.76</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -11460,24 +11460,24 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Intereses tarjeta crédito</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>4230</v>
+        <v>4130</v>
       </c>
       <c r="E231" t="n">
-        <v>4171160.15</v>
+        <v>4728471.71</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -11486,17 +11486,17 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>tarjetas.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -11508,7 +11508,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11518,14 +11518,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E232" t="n">
-        <v>4665656.44</v>
+        <v>4400704.74</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -11534,12 +11534,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11556,7 +11556,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E233" t="n">
-        <v>796930.42</v>
+        <v>1642076.26</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11621,7 +11621,7 @@
         <v>4130</v>
       </c>
       <c r="E234" t="n">
-        <v>2367461.18</v>
+        <v>652368.78</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11652,7 +11652,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11662,14 +11662,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Comisiones por cambio FX</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>4130</v>
+        <v>4210</v>
       </c>
       <c r="E235" t="n">
-        <v>2911083.68</v>
+        <v>2636827.79</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11700,7 +11700,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11710,14 +11710,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Comisiones por cambio FX</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>4130</v>
+        <v>4210</v>
       </c>
       <c r="E236" t="n">
-        <v>981062.92</v>
+        <v>2307673.49</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -11726,12 +11726,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11748,7 +11748,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11765,7 +11765,7 @@
         <v>4130</v>
       </c>
       <c r="E237" t="n">
-        <v>3614973.5</v>
+        <v>347470.12</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -11774,12 +11774,12 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11796,7 +11796,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E238" t="n">
-        <v>1899435.91</v>
+        <v>3110584.24</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11854,14 +11854,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E239" t="n">
-        <v>1683507.73</v>
+        <v>774307.88</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11892,7 +11892,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11909,7 +11909,7 @@
         <v>4210</v>
       </c>
       <c r="E240" t="n">
-        <v>3266632.55</v>
+        <v>894180.58</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11940,7 +11940,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E241" t="n">
-        <v>4740042.61</v>
+        <v>483238.29</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -11966,12 +11966,12 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11988,7 +11988,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -11998,14 +11998,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E242" t="n">
-        <v>4244288.36</v>
+        <v>1181271.42</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12036,7 +12036,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12046,14 +12046,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Comisiones por cambio FX</t>
+          <t>Spread financiero</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>4130</v>
+        <v>4210</v>
       </c>
       <c r="E243" t="n">
-        <v>561709.38</v>
+        <v>661888.37</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -12084,7 +12084,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12101,7 +12101,7 @@
         <v>4130</v>
       </c>
       <c r="E244" t="n">
-        <v>4425606</v>
+        <v>288825.02</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -12110,12 +12110,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12132,7 +12132,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12142,14 +12142,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por cambio FX</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="E245" t="n">
-        <v>3388125.65</v>
+        <v>2978247.61</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -12158,12 +12158,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12180,7 +12180,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12197,7 +12197,7 @@
         <v>4210</v>
       </c>
       <c r="E246" t="n">
-        <v>1696985.84</v>
+        <v>3139406.09</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -12206,12 +12206,12 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12220,1254 +12220,6 @@
         </is>
       </c>
       <c r="J246" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E247" t="n">
-        <v>4390186.28</v>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E248" t="n">
-        <v>1735882.89</v>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E249" t="n">
-        <v>736957.61</v>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E250" t="n">
-        <v>4980240.9</v>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E251" t="n">
-        <v>1831652.89</v>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E252" t="n">
-        <v>1242302.43</v>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E253" t="n">
-        <v>3324582.34</v>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E254" t="n">
-        <v>113230.09</v>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E255" t="n">
-        <v>1255816.07</v>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E256" t="n">
-        <v>2832871.76</v>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E257" t="n">
-        <v>4728471.71</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E258" t="n">
-        <v>4400704.74</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E259" t="n">
-        <v>1642076.26</v>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E260" t="n">
-        <v>652368.78</v>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E261" t="n">
-        <v>2636827.79</v>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E262" t="n">
-        <v>2307673.49</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E263" t="n">
-        <v>347470.12</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E264" t="n">
-        <v>3110584.24</v>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E265" t="n">
-        <v>774307.88</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E266" t="n">
-        <v>894180.58</v>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E267" t="n">
-        <v>483238.29</v>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E268" t="n">
-        <v>1181271.42</v>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E269" t="n">
-        <v>661888.37</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E270" t="n">
-        <v>288825.02</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Comisiones por cambio FX</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>4130</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2978247.61</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Spread financiero</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>4210</v>
-      </c>
-      <c r="E272" t="n">
-        <v>3139406.09</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
         <is>
           <t>Ingreso</t>
         </is>
@@ -13484,7 +12236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13667,147 +12419,107 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38106584.01</v>
+        <v>35924701.34</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Banca Corporativa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ingreso por asesoría</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35127631.16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spread financiero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>32382954.61</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Tarjetas</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ingreso por anualidad</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>35924701.34</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ingreso por asesoría</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>35127631.16</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spread financiero</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32382954.61</v>
+        <v>31955094.22</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Banca Comercial</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Comisiones por apertura</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31955094.22</v>
+        <v>28803533.4</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Banca Corporativa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Comisiones por apertura</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28803533.4</v>
+        <v>24834656.5</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Comisiones por apertura</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>24834656.5</v>
-      </c>
-      <c r="D17" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Comisiones por manejo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>24550420.87</v>
-      </c>
-      <c r="D18" t="n">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:A14"/>
+  <mergeCells count="3">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
